--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>76.00136254257598</v>
+        <v>12.3502214131686</v>
       </c>
       <c r="D2" t="n">
-        <v>76.04681150840129</v>
+        <v>12.35760687011521</v>
       </c>
       <c r="E2" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F2" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.41753411010325</v>
+        <v>8.030349292891778</v>
       </c>
       <c r="D3" t="n">
-        <v>49.52834282939816</v>
+        <v>8.048355709777201</v>
       </c>
       <c r="E3" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F3" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.40272677839796</v>
+        <v>10.30294310148967</v>
       </c>
       <c r="D4" t="n">
-        <v>63.51112570563285</v>
+        <v>10.32055792716534</v>
       </c>
       <c r="E4" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F4" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.64686689572933</v>
+        <v>6.442615870556017</v>
       </c>
       <c r="D5" t="n">
-        <v>39.75463374065863</v>
+        <v>6.460127982857027</v>
       </c>
       <c r="E5" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F5" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.31468822982078</v>
+        <v>5.576136837345877</v>
       </c>
       <c r="D6" t="n">
-        <v>34.35821149012889</v>
+        <v>5.583209367145945</v>
       </c>
       <c r="E6" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F6" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>52.62049536965713</v>
+        <v>8.550830497569283</v>
       </c>
       <c r="D7" t="n">
-        <v>52.65234234651327</v>
+        <v>8.556005631308407</v>
       </c>
       <c r="E7" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F7" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.88599365209038</v>
+        <v>6.968973968464688</v>
       </c>
       <c r="D8" t="n">
-        <v>42.99593110260101</v>
+        <v>6.986838804172665</v>
       </c>
       <c r="E8" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F8" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.45148032261978</v>
+        <v>4.135865552425714</v>
       </c>
       <c r="D9" t="n">
-        <v>25.51246434575946</v>
+        <v>4.145775456185913</v>
       </c>
       <c r="E9" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F9" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.11913764128069</v>
+        <v>4.406859866708112</v>
       </c>
       <c r="D10" t="n">
-        <v>27.14359130999225</v>
+        <v>4.41083358787374</v>
       </c>
       <c r="E10" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F10" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>22.77659281083577</v>
+        <v>3.701196331760812</v>
       </c>
       <c r="D11" t="n">
-        <v>22.86016469131997</v>
+        <v>3.714776762339496</v>
       </c>
       <c r="E11" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F11" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>27.26592247845183</v>
+        <v>4.430712402748423</v>
       </c>
       <c r="D12" t="n">
-        <v>27.37581376140098</v>
+        <v>4.448569736227659</v>
       </c>
       <c r="E12" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F12" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>46.83847955900272</v>
+        <v>7.611252928337942</v>
       </c>
       <c r="D13" t="n">
-        <v>46.93722964824541</v>
+        <v>7.627299817839878</v>
       </c>
       <c r="E13" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F13" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>14.05366282470032</v>
+        <v>2.283720209013802</v>
       </c>
       <c r="D14" t="n">
-        <v>14.14018357985533</v>
+        <v>2.297779831726491</v>
       </c>
       <c r="E14" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F14" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>41.84406553325048</v>
+        <v>6.799660649153203</v>
       </c>
       <c r="D15" t="n">
-        <v>41.77803392799844</v>
+        <v>6.788930513299747</v>
       </c>
       <c r="E15" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F15" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>5.966920235010027</v>
+        <v>0.9696245381891295</v>
       </c>
       <c r="D16" t="n">
-        <v>6.076831733080506</v>
+        <v>0.9874851566255822</v>
       </c>
       <c r="E16" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F16" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>64.10024408219066</v>
+        <v>10.41628966335598</v>
       </c>
       <c r="D17" t="n">
-        <v>64.17329043555635</v>
+        <v>10.42815969577791</v>
       </c>
       <c r="E17" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F17" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>41.84269821551245</v>
+        <v>6.799438460020773</v>
       </c>
       <c r="D18" t="n">
-        <v>41.91740773167579</v>
+        <v>6.811578756397315</v>
       </c>
       <c r="E18" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F18" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>11.60626335130229</v>
+        <v>1.886017794586622</v>
       </c>
       <c r="D19" t="n">
-        <v>11.50937276983638</v>
+        <v>1.870273075098411</v>
       </c>
       <c r="E19" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F19" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>24.32931577763857</v>
+        <v>3.953513813866268</v>
       </c>
       <c r="D20" t="n">
-        <v>24.35121025836767</v>
+        <v>3.957071666984746</v>
       </c>
       <c r="E20" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F20" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>52.52627255160265</v>
+        <v>8.535519289635431</v>
       </c>
       <c r="D21" t="n">
-        <v>52.42683830047906</v>
+        <v>8.519361223827849</v>
       </c>
       <c r="E21" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F21" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>38.72450759880314</v>
+        <v>6.292732484805511</v>
       </c>
       <c r="D22" t="n">
-        <v>38.74991828860541</v>
+        <v>6.296861721898379</v>
       </c>
       <c r="E22" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F22" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>64.67885399560315</v>
+        <v>10.51031377428551</v>
       </c>
       <c r="D23" t="n">
-        <v>64.71434886237734</v>
+        <v>10.51608169013632</v>
       </c>
       <c r="E23" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F23" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>27.23683683802667</v>
+        <v>4.425985986179334</v>
       </c>
       <c r="D24" t="n">
-        <v>27.15137876482367</v>
+        <v>4.412099049283846</v>
       </c>
       <c r="E24" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F24" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>34.36643840015917</v>
+        <v>5.584546240025865</v>
       </c>
       <c r="D25" t="n">
-        <v>34.29714072829157</v>
+        <v>5.573285368347381</v>
       </c>
       <c r="E25" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F25" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>55.75374139448152</v>
+        <v>9.059982976603248</v>
       </c>
       <c r="D26" t="n">
-        <v>55.76309227258353</v>
+        <v>9.061502494294825</v>
       </c>
       <c r="E26" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F26" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>39.18071721849597</v>
+        <v>6.366866548005595</v>
       </c>
       <c r="D27" t="n">
-        <v>39.07727784801791</v>
+        <v>6.35005765030291</v>
       </c>
       <c r="E27" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F27" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>64.85881894371889</v>
+        <v>10.53955807835432</v>
       </c>
       <c r="D28" t="n">
-        <v>64.74888153169699</v>
+        <v>10.52169324890076</v>
       </c>
       <c r="E28" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F28" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>55.71533395877599</v>
+        <v>9.0537417683011</v>
       </c>
       <c r="D29" t="n">
-        <v>55.70045776496394</v>
+        <v>9.051324386806639</v>
       </c>
       <c r="E29" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F29" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>49.4865051462703</v>
+        <v>8.041557086268925</v>
       </c>
       <c r="D30" t="n">
-        <v>49.38196835820393</v>
+        <v>8.024569858208139</v>
       </c>
       <c r="E30" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F30" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>47.54387044859651</v>
+        <v>7.725878947896932</v>
       </c>
       <c r="D31" t="n">
-        <v>47.45769039288867</v>
+        <v>7.71187468884441</v>
       </c>
       <c r="E31" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F31" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>58.25147752307752</v>
+        <v>9.465865097500098</v>
       </c>
       <c r="D32" t="n">
-        <v>58.15167830443058</v>
+        <v>9.449647724469969</v>
       </c>
       <c r="E32" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F32" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>74.67577093972682</v>
+        <v>12.13481277770561</v>
       </c>
       <c r="D33" t="n">
-        <v>74.56517354889746</v>
+        <v>12.11684070169584</v>
       </c>
       <c r="E33" t="n">
-        <v>17.64757719564831</v>
+        <v>2.86773129429285</v>
       </c>
       <c r="F33" t="n">
-        <v>17.63105983514211</v>
+        <v>2.865047223210594</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
